--- a/data/trans_orig/IP07A15-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A15-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2007 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2007 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>37233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28300</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42414</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57186</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75949</t>
+          <t>76045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29515</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>42994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52876</t>
+          <t>53715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72314</t>
+          <t>73769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43864</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>59810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57067</t>
+          <t>56879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88884</t>
+          <t>91504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112196</t>
+          <t>113228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>35402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51563</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>28703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43895</t>
+          <t>43349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67780</t>
+          <t>67781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91039</t>
+          <t>89485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18234</t>
+          <t>18700</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>40163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>26926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40294</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59365</t>
+          <t>59360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76068</t>
+          <t>76435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,32%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27340</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31115</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37937</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53334</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32320</t>
+          <t>32530</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48891</t>
+          <t>48391</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36879</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74315</t>
+          <t>74291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96825</t>
+          <t>97772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,7%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28999</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45685</t>
+          <t>45811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35050</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>51499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69012</t>
+          <t>68578</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>90885</t>
+          <t>91342</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32312</t>
+          <t>30933</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>143320</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>173446</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>149774</t>
+          <t>149671</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>178783</t>
+          <t>177654</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>303180</t>
+          <t>298946</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>343844</t>
+          <t>341740</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>114229</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>141400</t>
+          <t>142264</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>123813</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>154051</t>
+          <t>153391</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>245882</t>
+          <t>247523</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>288973</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>54807</t>
+          <t>54271</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>81958</t>
+          <t>78720</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2012 (tasa de respuesta: 97,71%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30633</t>
+          <t>30875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44631</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>28440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42804</t>
+          <t>42730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63444</t>
+          <t>64458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83683</t>
+          <t>84053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25674</t>
+          <t>25786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>35912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38618</t>
+          <t>38295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>56947</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49218</t>
+          <t>49371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>64431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>43221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>58835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97121</t>
+          <t>96814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119678</t>
+          <t>118806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -5169,47 +5169,47 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>39145</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>38905</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>38905</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31798</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47363</t>
+          <t>46745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60010</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81487</t>
+          <t>81937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>23942</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>29739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42374</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38231</t>
+          <t>38387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50766</t>
+          <t>50668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71498</t>
+          <t>71499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89451</t>
+          <t>89240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31184</t>
+          <t>30534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52748</t>
+          <t>51598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36723</t>
+          <t>36537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52441</t>
+          <t>51790</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37470</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>54042</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79260</t>
+          <t>78386</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101544</t>
+          <t>101423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44111</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27658</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>42828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60086</t>
+          <t>60659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82375</t>
+          <t>82053</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>158662</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190536</t>
+          <t>189005</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161342</t>
+          <t>161523</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>190949</t>
+          <t>190825</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>333256</t>
+          <t>332480</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>373581</t>
+          <t>373666</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>95769</t>
+          <t>97487</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>124692</t>
+          <t>124981</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>107400</t>
+          <t>108297</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>137014</t>
+          <t>137129</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>212155</t>
+          <t>212380</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>252264</t>
+          <t>251701</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44483</t>
+          <t>42902</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50336</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>75043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>28795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>43324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34925</t>
+          <t>34983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49732</t>
+          <t>49851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68909</t>
+          <t>67289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89022</t>
+          <t>88240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,37%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34712</t>
+          <t>34741</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40793</t>
+          <t>41342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59686</t>
+          <t>61462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48923</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65383</t>
+          <t>64837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50929</t>
+          <t>51594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>67634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105009</t>
+          <t>105449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127826</t>
+          <t>128941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33279</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49728</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>28431</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44488</t>
+          <t>44611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66492</t>
+          <t>66127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88701</t>
+          <t>88795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36437</t>
+          <t>35963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49359</t>
+          <t>49012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>30689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45266</t>
+          <t>45658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71408</t>
+          <t>71712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91284</t>
+          <t>91441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>29985</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23669</t>
+          <t>24030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43394</t>
+          <t>43398</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>62919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46907</t>
+          <t>46989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64806</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47190</t>
+          <t>46153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62966</t>
+          <t>63040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97770</t>
+          <t>96816</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>123419</t>
+          <t>122094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>33208</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50352</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32293</t>
+          <t>31563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47501</t>
+          <t>48476</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69153</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>92647</t>
+          <t>93912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15372</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11490</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>23742</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>177106</t>
+          <t>175656</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207296</t>
+          <t>207277</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>210791</t>
+          <t>209968</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>365682</t>
+          <t>364597</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>408658</t>
+          <t>408245</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,18%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114167</t>
+          <t>112328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143451</t>
+          <t>143418</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>118516</t>
+          <t>119256</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>148567</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>241959</t>
+          <t>240870</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>282592</t>
+          <t>283003</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>40988</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>44993</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68704</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
